--- a/data/nzd0182/nzd0182.xlsx
+++ b/data/nzd0182/nzd0182.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I588"/>
+  <dimension ref="A1:I593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19742,10 +19742,10 @@
         <v>376.25</v>
       </c>
       <c r="E588" t="n">
-        <v>388.68</v>
+        <v>386.51</v>
       </c>
       <c r="F588" t="n">
-        <v>392.76</v>
+        <v>389.58</v>
       </c>
       <c r="G588" t="n">
         <v>392.59</v>
@@ -19754,6 +19754,171 @@
         <v>394.06</v>
       </c>
       <c r="I588" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>467.4</v>
+      </c>
+      <c r="C589" t="n">
+        <v>369.44</v>
+      </c>
+      <c r="D589" t="n">
+        <v>376.07</v>
+      </c>
+      <c r="E589" t="n">
+        <v>386.56</v>
+      </c>
+      <c r="F589" t="n">
+        <v>389.61</v>
+      </c>
+      <c r="G589" t="n">
+        <v>392.76</v>
+      </c>
+      <c r="H589" t="n">
+        <v>392.78</v>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>469.74</v>
+      </c>
+      <c r="C590" t="n">
+        <v>368.23</v>
+      </c>
+      <c r="D590" t="n">
+        <v>372.89</v>
+      </c>
+      <c r="E590" t="n">
+        <v>381.84</v>
+      </c>
+      <c r="F590" t="n">
+        <v>385.18</v>
+      </c>
+      <c r="G590" t="n">
+        <v>387.69</v>
+      </c>
+      <c r="H590" t="n">
+        <v>388.59</v>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:53+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>473.64</v>
+      </c>
+      <c r="C591" t="n">
+        <v>368.23</v>
+      </c>
+      <c r="D591" t="n">
+        <v>372.89</v>
+      </c>
+      <c r="E591" t="n">
+        <v>382.46</v>
+      </c>
+      <c r="F591" t="n">
+        <v>385.18</v>
+      </c>
+      <c r="G591" t="n">
+        <v>387.69</v>
+      </c>
+      <c r="H591" t="n">
+        <v>388.59</v>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>473.64</v>
+      </c>
+      <c r="C592" t="n">
+        <v>367.71</v>
+      </c>
+      <c r="D592" t="n">
+        <v>371.88</v>
+      </c>
+      <c r="E592" t="n">
+        <v>381.77</v>
+      </c>
+      <c r="F592" t="n">
+        <v>384.31</v>
+      </c>
+      <c r="G592" t="n">
+        <v>387.64</v>
+      </c>
+      <c r="H592" t="n">
+        <v>388.94</v>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>479.41</v>
+      </c>
+      <c r="C593" t="n">
+        <v>367.88</v>
+      </c>
+      <c r="D593" t="n">
+        <v>371.66</v>
+      </c>
+      <c r="E593" t="n">
+        <v>380.79</v>
+      </c>
+      <c r="F593" t="n">
+        <v>383.44</v>
+      </c>
+      <c r="G593" t="n">
+        <v>386.42</v>
+      </c>
+      <c r="H593" t="n">
+        <v>387.94</v>
+      </c>
+      <c r="I593" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19770,7 +19935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B635"/>
+  <dimension ref="A1:B641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26123,6 +26288,66 @@
       </c>
       <c r="B635" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>
@@ -26291,28 +26516,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07050089209738844</v>
+        <v>0.09828615538980755</v>
       </c>
       <c r="J2" t="n">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K2" t="n">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002061885014211784</v>
+        <v>0.0004074254684847123</v>
       </c>
       <c r="M2" t="n">
-        <v>31.49253445874027</v>
+        <v>31.36222949773684</v>
       </c>
       <c r="N2" t="n">
-        <v>1516.694090762736</v>
+        <v>1505.743376084689</v>
       </c>
       <c r="O2" t="n">
-        <v>38.94475690979128</v>
+        <v>38.80390928868751</v>
       </c>
       <c r="P2" t="n">
-        <v>453.6324467209404</v>
+        <v>453.3528198538144</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26369,28 +26594,28 @@
         <v>0.0462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8590762014858191</v>
+        <v>0.8961253655281639</v>
       </c>
       <c r="J3" t="n">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K3" t="n">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2987481740091792</v>
+        <v>0.3118418190160854</v>
       </c>
       <c r="M3" t="n">
-        <v>8.428770000605729</v>
+        <v>8.566863054062191</v>
       </c>
       <c r="N3" t="n">
-        <v>104.6835730256184</v>
+        <v>108.203159792849</v>
       </c>
       <c r="O3" t="n">
-        <v>10.23149906052962</v>
+        <v>10.4020747830829</v>
       </c>
       <c r="P3" t="n">
-        <v>321.9821686792847</v>
+        <v>321.6060588091505</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26447,28 +26672,28 @@
         <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9291810651955237</v>
+        <v>0.9731577553461128</v>
       </c>
       <c r="J4" t="n">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K4" t="n">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3143035072923703</v>
+        <v>0.3268929253518672</v>
       </c>
       <c r="M4" t="n">
-        <v>8.165538063317026</v>
+        <v>8.394674179900901</v>
       </c>
       <c r="N4" t="n">
-        <v>113.1437986271641</v>
+        <v>118.3599644691689</v>
       </c>
       <c r="O4" t="n">
-        <v>10.63690738077399</v>
+        <v>10.87933658221718</v>
       </c>
       <c r="P4" t="n">
-        <v>320.677884779503</v>
+        <v>320.2292987605877</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26525,28 +26750,28 @@
         <v>0.057</v>
       </c>
       <c r="I5" t="n">
-        <v>1.056779610928006</v>
+        <v>1.103106419585955</v>
       </c>
       <c r="J5" t="n">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K5" t="n">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="L5" t="n">
-        <v>0.381258101170078</v>
+        <v>0.3915617281975114</v>
       </c>
       <c r="M5" t="n">
-        <v>7.750000588810722</v>
+        <v>7.951940592524882</v>
       </c>
       <c r="N5" t="n">
-        <v>108.8168586356879</v>
+        <v>114.712951373453</v>
       </c>
       <c r="O5" t="n">
-        <v>10.43153194098009</v>
+        <v>10.71041322141462</v>
       </c>
       <c r="P5" t="n">
-        <v>324.9379981303533</v>
+        <v>324.4655987570441</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26603,28 +26828,28 @@
         <v>0.0359</v>
       </c>
       <c r="I6" t="n">
-        <v>1.050930392226737</v>
+        <v>1.094775917599227</v>
       </c>
       <c r="J6" t="n">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K6" t="n">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3136585604474601</v>
+        <v>0.3265522236426182</v>
       </c>
       <c r="M6" t="n">
-        <v>9.578613730106049</v>
+        <v>9.721178753328291</v>
       </c>
       <c r="N6" t="n">
-        <v>145.1001521521914</v>
+        <v>149.9557387944704</v>
       </c>
       <c r="O6" t="n">
-        <v>12.04575245271923</v>
+        <v>12.24564162445033</v>
       </c>
       <c r="P6" t="n">
-        <v>329.2930016141845</v>
+        <v>328.8459001548037</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26681,28 +26906,28 @@
         <v>0.0523</v>
       </c>
       <c r="I7" t="n">
-        <v>1.112637245304994</v>
+        <v>1.169191476892875</v>
       </c>
       <c r="J7" t="n">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K7" t="n">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2596534395070536</v>
+        <v>0.2734347036094633</v>
       </c>
       <c r="M7" t="n">
-        <v>11.5133212814621</v>
+        <v>11.74864576500527</v>
       </c>
       <c r="N7" t="n">
-        <v>212.9807554652641</v>
+        <v>221.4611822364656</v>
       </c>
       <c r="O7" t="n">
-        <v>14.59386019753732</v>
+        <v>14.88157190072559</v>
       </c>
       <c r="P7" t="n">
-        <v>323.1080360977242</v>
+        <v>322.5336381744904</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26759,28 +26984,28 @@
         <v>0.0454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.217740766926371</v>
+        <v>1.268132248797432</v>
       </c>
       <c r="J8" t="n">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K8" t="n">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2689075519639789</v>
+        <v>0.282248002312273</v>
       </c>
       <c r="M8" t="n">
-        <v>12.40205458613409</v>
+        <v>12.52562886269956</v>
       </c>
       <c r="N8" t="n">
-        <v>242.0560140658578</v>
+        <v>248.1041158962767</v>
       </c>
       <c r="O8" t="n">
-        <v>15.55814944220095</v>
+        <v>15.75132108415915</v>
       </c>
       <c r="P8" t="n">
-        <v>325.1807376668769</v>
+        <v>324.6669022534663</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26818,7 +27043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I588"/>
+  <dimension ref="A1:I593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54253,12 +54478,12 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>-36.88368416980482,174.4371920688761</t>
+          <t>-36.88367904004234,174.4372155631072</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>-36.88301836385222,174.43689007903185</t>
+          <t>-36.88300970892275,174.43692409152035</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
@@ -54272,6 +54497,241 @@
         </is>
       </c>
       <c r="I588" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>-36.885938102788025,174.43690446289236</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>-36.88503912806706,174.43778362973356</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>-36.88435059270657,174.43751892061306</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>-36.88367915823969,174.4372150217655</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>-36.88300979057308,174.43692377064784</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>-36.88234361659581,174.43663108959683</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>-36.881689716622105,174.4363019178469</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>-36.88594281098844,174.4368788707651</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>-36.885036693380364,174.43779686308042</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>-36.884344194167475,174.43755369886736</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>-36.88366800039974,174.4372661244136</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>-36.88299773353283,174.43697115281205</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>-36.88232795857496,174.4366845283692</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>-36.88167530053203,174.43634536679696</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:53+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>-36.88595065797705,174.43683621721232</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>-36.885036693380364,174.43779686308042</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>-36.884344194167475,174.43755369886736</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>-36.88366946604945,174.4372594117785</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>-36.88299773353283,174.43697115281205</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>-36.88232795857496,174.4366845283692</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>-36.88167530053203,174.43634536679696</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>-36.88595065797705,174.43683621721232</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>-36.88503564706826,174.43780255013831</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>-36.88434216192497,174.43756474478963</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>-36.88366783492313,174.43726688229177</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>-36.88299536566948,174.43698045811107</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>-36.882327804156496,174.4366850553787</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>-36.881676504740625,174.43634173741034</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>-36.88596226746829,174.43677311181088</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>-36.885035989131865,174.43780069090786</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>-36.88434171925814,174.43756715083202</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>-36.88366551825018,174.43727749258534</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>-36.88299299780539,174.4369897634095</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>-36.88232403634513,174.43669791440925</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>-36.88167306414435,174.43635210708604</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0182/nzd0182.xlsx
+++ b/data/nzd0182/nzd0182.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I593"/>
+  <dimension ref="A1:I594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19921,6 +19921,39 @@
       <c r="I593" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>479.28</v>
+      </c>
+      <c r="C594" t="n">
+        <v>365.89</v>
+      </c>
+      <c r="D594" t="n">
+        <v>368.37</v>
+      </c>
+      <c r="E594" t="n">
+        <v>375.78</v>
+      </c>
+      <c r="F594" t="n">
+        <v>378.68</v>
+      </c>
+      <c r="G594" t="n">
+        <v>380.99</v>
+      </c>
+      <c r="H594" t="n">
+        <v>384.01</v>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -19935,7 +19968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B641"/>
+  <dimension ref="A1:B642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26348,6 +26381,16 @@
       </c>
       <c r="B641" t="n">
         <v>0.92</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -26516,28 +26559,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09828615538980755</v>
+        <v>0.1057931698563373</v>
       </c>
       <c r="J2" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K2" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004074254684847123</v>
+        <v>0.0004734447992315038</v>
       </c>
       <c r="M2" t="n">
-        <v>31.36222949773684</v>
+        <v>31.34703130046893</v>
       </c>
       <c r="N2" t="n">
-        <v>1505.743376084689</v>
+        <v>1503.997280152009</v>
       </c>
       <c r="O2" t="n">
-        <v>38.80390928868751</v>
+        <v>38.78140379295223</v>
       </c>
       <c r="P2" t="n">
-        <v>453.3528198538144</v>
+        <v>453.2770193816454</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26594,28 +26637,28 @@
         <v>0.0462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8961253655281639</v>
+        <v>0.9025485968744671</v>
       </c>
       <c r="J3" t="n">
+        <v>593</v>
+      </c>
+      <c r="K3" t="n">
         <v>592</v>
       </c>
-      <c r="K3" t="n">
-        <v>591</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.3118418190160854</v>
+        <v>0.3143808286870873</v>
       </c>
       <c r="M3" t="n">
-        <v>8.566863054062191</v>
+        <v>8.589734182656951</v>
       </c>
       <c r="N3" t="n">
-        <v>108.203159792849</v>
+        <v>108.694190085932</v>
       </c>
       <c r="O3" t="n">
-        <v>10.4020747830829</v>
+        <v>10.42565058334164</v>
       </c>
       <c r="P3" t="n">
-        <v>321.6060588091505</v>
+        <v>321.5406370149232</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26672,28 +26715,28 @@
         <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9731577553461128</v>
+        <v>0.9801845384879073</v>
       </c>
       <c r="J4" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K4" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3268929253518672</v>
+        <v>0.329403757878614</v>
       </c>
       <c r="M4" t="n">
-        <v>8.394674179900901</v>
+        <v>8.429028572207168</v>
       </c>
       <c r="N4" t="n">
-        <v>118.3599644691689</v>
+        <v>118.959670287446</v>
       </c>
       <c r="O4" t="n">
-        <v>10.87933658221718</v>
+        <v>10.90686344864765</v>
       </c>
       <c r="P4" t="n">
-        <v>320.2292987605877</v>
+        <v>320.157383957297</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26750,28 +26793,28 @@
         <v>0.057</v>
       </c>
       <c r="I5" t="n">
-        <v>1.103106419585955</v>
+        <v>1.110017879650961</v>
       </c>
       <c r="J5" t="n">
+        <v>593</v>
+      </c>
+      <c r="K5" t="n">
         <v>592</v>
       </c>
-      <c r="K5" t="n">
-        <v>591</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.3915617281975114</v>
+        <v>0.3938306233098282</v>
       </c>
       <c r="M5" t="n">
-        <v>7.951940592524882</v>
+        <v>7.979047182745683</v>
       </c>
       <c r="N5" t="n">
-        <v>114.712951373453</v>
+        <v>115.2922163683549</v>
       </c>
       <c r="O5" t="n">
-        <v>10.71041322141462</v>
+        <v>10.73742130906462</v>
       </c>
       <c r="P5" t="n">
-        <v>324.4655987570441</v>
+        <v>324.394890554231</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26828,28 +26871,28 @@
         <v>0.0359</v>
       </c>
       <c r="I6" t="n">
-        <v>1.094775917599227</v>
+        <v>1.10128461855768</v>
       </c>
       <c r="J6" t="n">
+        <v>593</v>
+      </c>
+      <c r="K6" t="n">
         <v>592</v>
       </c>
-      <c r="K6" t="n">
-        <v>591</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.3265522236426182</v>
+        <v>0.328983791232286</v>
       </c>
       <c r="M6" t="n">
-        <v>9.721178753328291</v>
+        <v>9.737956591140204</v>
       </c>
       <c r="N6" t="n">
-        <v>149.9557387944704</v>
+        <v>150.388001132935</v>
       </c>
       <c r="O6" t="n">
-        <v>12.24564162445033</v>
+        <v>12.26327856378281</v>
       </c>
       <c r="P6" t="n">
-        <v>328.8459001548037</v>
+        <v>328.7793124087862</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26906,28 +26949,28 @@
         <v>0.0523</v>
       </c>
       <c r="I7" t="n">
-        <v>1.169191476892875</v>
+        <v>1.177792669365692</v>
       </c>
       <c r="J7" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K7" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2734347036094633</v>
+        <v>0.2760173922663854</v>
       </c>
       <c r="M7" t="n">
-        <v>11.74864576500527</v>
+        <v>11.78049470449307</v>
       </c>
       <c r="N7" t="n">
-        <v>221.4611822364656</v>
+        <v>222.293444219189</v>
       </c>
       <c r="O7" t="n">
-        <v>14.88157190072559</v>
+        <v>14.90950851702326</v>
       </c>
       <c r="P7" t="n">
-        <v>322.5336381744904</v>
+        <v>322.4459886582471</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26984,28 +27027,28 @@
         <v>0.0454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.268132248797432</v>
+        <v>1.276192181041174</v>
       </c>
       <c r="J8" t="n">
+        <v>593</v>
+      </c>
+      <c r="K8" t="n">
         <v>592</v>
       </c>
-      <c r="K8" t="n">
-        <v>591</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.282248002312273</v>
+        <v>0.2847230964074732</v>
       </c>
       <c r="M8" t="n">
-        <v>12.52562886269956</v>
+        <v>12.54164353120174</v>
       </c>
       <c r="N8" t="n">
-        <v>248.1041158962767</v>
+        <v>248.7363131679054</v>
       </c>
       <c r="O8" t="n">
-        <v>15.75132108415915</v>
+        <v>15.77137638787133</v>
       </c>
       <c r="P8" t="n">
-        <v>324.6669022534663</v>
+        <v>324.5844445211798</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27043,7 +27086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I593"/>
+  <dimension ref="A1:I594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54737,6 +54780,53 @@
         </is>
       </c>
     </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>-36.885962005903004,174.43677453359658</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>-36.885031984973836,174.43782245483962</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>-36.88433509937131,174.4376031320988</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>-36.88365367483614,174.4373317349941</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>-36.88298004258232,174.43704067514682</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>-36.88230726647963,174.43675514761964</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>-36.88165954259236,174.43639285990218</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0182/nzd0182.xlsx
+++ b/data/nzd0182/nzd0182.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I594"/>
+  <dimension ref="A1:I595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19952,6 +19952,39 @@
         <v>384.01</v>
       </c>
       <c r="I594" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>482.21</v>
+      </c>
+      <c r="C595" t="n">
+        <v>363.21</v>
+      </c>
+      <c r="D595" t="n">
+        <v>365.78</v>
+      </c>
+      <c r="E595" t="n">
+        <v>371.43</v>
+      </c>
+      <c r="F595" t="n">
+        <v>374.63</v>
+      </c>
+      <c r="G595" t="n">
+        <v>373.96</v>
+      </c>
+      <c r="H595" t="n">
+        <v>377.17</v>
+      </c>
+      <c r="I595" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -19968,7 +20001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B642"/>
+  <dimension ref="A1:B643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26391,6 +26424,16 @@
       </c>
       <c r="B642" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -26559,28 +26602,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1057931698563373</v>
+        <v>0.1142190541555242</v>
       </c>
       <c r="J2" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="K2" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004734447992315038</v>
+        <v>0.000553423396749686</v>
       </c>
       <c r="M2" t="n">
-        <v>31.34703130046893</v>
+        <v>31.33660626361185</v>
       </c>
       <c r="N2" t="n">
-        <v>1503.997280152009</v>
+        <v>1502.504209178945</v>
       </c>
       <c r="O2" t="n">
-        <v>38.78140379295223</v>
+        <v>38.76214918163007</v>
       </c>
       <c r="P2" t="n">
-        <v>453.2770193816454</v>
+        <v>453.1915805898354</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26637,28 +26680,28 @@
         <v>0.0462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9025485968744671</v>
+        <v>0.9080621569093745</v>
       </c>
       <c r="J3" t="n">
+        <v>594</v>
+      </c>
+      <c r="K3" t="n">
         <v>593</v>
       </c>
-      <c r="K3" t="n">
-        <v>592</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.3143808286870873</v>
+        <v>0.3168456564124583</v>
       </c>
       <c r="M3" t="n">
-        <v>8.589734182656951</v>
+        <v>8.607108421115283</v>
       </c>
       <c r="N3" t="n">
-        <v>108.694190085932</v>
+        <v>109.0044787341246</v>
       </c>
       <c r="O3" t="n">
-        <v>10.42565058334164</v>
+        <v>10.44052099917071</v>
       </c>
       <c r="P3" t="n">
-        <v>321.5406370149232</v>
+        <v>321.4842630429135</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26715,28 +26758,28 @@
         <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9801845384879073</v>
+        <v>0.9863231640522157</v>
       </c>
       <c r="J4" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="K4" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L4" t="n">
-        <v>0.329403757878614</v>
+        <v>0.3318747961004925</v>
       </c>
       <c r="M4" t="n">
-        <v>8.429028572207168</v>
+        <v>8.457554753439737</v>
       </c>
       <c r="N4" t="n">
-        <v>118.959670287446</v>
+        <v>119.3656920209704</v>
       </c>
       <c r="O4" t="n">
-        <v>10.90686344864765</v>
+        <v>10.92546072351049</v>
       </c>
       <c r="P4" t="n">
-        <v>320.157383957297</v>
+        <v>320.0943169944801</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26793,28 +26836,28 @@
         <v>0.057</v>
       </c>
       <c r="I5" t="n">
-        <v>1.110017879650961</v>
+        <v>1.115470079798211</v>
       </c>
       <c r="J5" t="n">
+        <v>594</v>
+      </c>
+      <c r="K5" t="n">
         <v>593</v>
       </c>
-      <c r="K5" t="n">
-        <v>592</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.3938306233098282</v>
+        <v>0.396084599619283</v>
       </c>
       <c r="M5" t="n">
-        <v>7.979047182745683</v>
+        <v>7.997455709027846</v>
       </c>
       <c r="N5" t="n">
-        <v>115.2922163683549</v>
+        <v>115.5760613323398</v>
       </c>
       <c r="O5" t="n">
-        <v>10.73742130906462</v>
+        <v>10.75063074113979</v>
       </c>
       <c r="P5" t="n">
-        <v>324.394890554231</v>
+        <v>324.3388970751481</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26871,28 +26914,28 @@
         <v>0.0359</v>
       </c>
       <c r="I6" t="n">
-        <v>1.10128461855768</v>
+        <v>1.106433699891661</v>
       </c>
       <c r="J6" t="n">
+        <v>594</v>
+      </c>
+      <c r="K6" t="n">
         <v>593</v>
       </c>
-      <c r="K6" t="n">
-        <v>592</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.328983791232286</v>
+        <v>0.3312552073122454</v>
       </c>
       <c r="M6" t="n">
-        <v>9.737956591140204</v>
+        <v>9.747556575344053</v>
       </c>
       <c r="N6" t="n">
-        <v>150.388001132935</v>
+        <v>150.5609617592089</v>
       </c>
       <c r="O6" t="n">
-        <v>12.26327856378281</v>
+        <v>12.2703285106475</v>
       </c>
       <c r="P6" t="n">
-        <v>328.7793124087862</v>
+        <v>328.7264319256445</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26949,28 +26992,28 @@
         <v>0.0523</v>
       </c>
       <c r="I7" t="n">
-        <v>1.177792669365692</v>
+        <v>1.18407014580145</v>
       </c>
       <c r="J7" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="K7" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2760173922663854</v>
+        <v>0.2783272983760984</v>
       </c>
       <c r="M7" t="n">
-        <v>11.78049470449307</v>
+        <v>11.79819841569416</v>
       </c>
       <c r="N7" t="n">
-        <v>222.293444219189</v>
+        <v>222.5577294601151</v>
       </c>
       <c r="O7" t="n">
-        <v>14.90950851702326</v>
+        <v>14.91836886057303</v>
       </c>
       <c r="P7" t="n">
-        <v>322.4459886582471</v>
+        <v>322.3817718188674</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27027,28 +27070,28 @@
         <v>0.0454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.276192181041174</v>
+        <v>1.281979243986453</v>
       </c>
       <c r="J8" t="n">
+        <v>594</v>
+      </c>
+      <c r="K8" t="n">
         <v>593</v>
       </c>
-      <c r="K8" t="n">
-        <v>592</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.2847230964074732</v>
+        <v>0.2868991575708527</v>
       </c>
       <c r="M8" t="n">
-        <v>12.54164353120174</v>
+        <v>12.54727595666381</v>
       </c>
       <c r="N8" t="n">
-        <v>248.7363131679054</v>
+        <v>248.8556783470954</v>
       </c>
       <c r="O8" t="n">
-        <v>15.77137638787133</v>
+        <v>15.77516016866692</v>
       </c>
       <c r="P8" t="n">
-        <v>324.5844445211798</v>
+        <v>324.5250120390209</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27086,7 +27129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I594"/>
+  <dimension ref="A1:I595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54827,6 +54870,53 @@
         </is>
       </c>
     </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>-36.885967901178276,174.43674248873185</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>-36.885026592433164,174.43785176505548</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>-36.88432988796347,174.43763145777228</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>-36.88364339161251,174.4373788316821</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>-36.88296901973907,174.4370839928924</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>-36.882285555177056,174.43682924508937</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>-36.88163600886619,174.43646378843252</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
